--- a/meu-projeto/docs/clientes/syra-digital/campaigns/data.xlsx
+++ b/meu-projeto/docs/clientes/syra-digital/campaigns/data.xlsx
@@ -102,7 +102,7 @@
     <t>120243183154170249</t>
   </si>
   <si>
-    <t>[Syra] Dra Gabrielle - Emagrecimento [Formulário Instantâneo] [CBO]</t>
+    <t>[Syra] Emagrecimento Publico Frio [Formulário Instantâneo] [ABO]</t>
   </si>
   <si>
     <t>10/03/2026</t>
@@ -863,7 +863,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>19</v>
@@ -1004,7 +1004,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
